--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.62643512985571</v>
+        <v>4.651795708601553</v>
       </c>
       <c r="D2" t="n">
-        <v>36.00917553181069</v>
+        <v>5.851491023919237</v>
       </c>
       <c r="E2" t="n">
-        <v>15.82582704376214</v>
+        <v>2.571696894611348</v>
       </c>
       <c r="F2" t="n">
-        <v>15.85860363360866</v>
+        <v>2.577023090461408</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.02185507187493</v>
+        <v>3.741051449179676</v>
       </c>
       <c r="D3" t="n">
-        <v>32.58224588260575</v>
+        <v>5.294614955923436</v>
       </c>
       <c r="E3" t="n">
-        <v>15.82582704376214</v>
+        <v>2.571696894611348</v>
       </c>
       <c r="F3" t="n">
-        <v>15.85860363360866</v>
+        <v>2.577023090461408</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.95158258501943</v>
+        <v>2.429632170065658</v>
       </c>
       <c r="D4" t="n">
-        <v>15.88752043450154</v>
+        <v>2.581722070606501</v>
       </c>
       <c r="E4" t="n">
-        <v>15.82582704376214</v>
+        <v>2.571696894611348</v>
       </c>
       <c r="F4" t="n">
-        <v>15.85860363360866</v>
+        <v>2.577023090461408</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.42084793394669</v>
+        <v>3.643387789266336</v>
       </c>
       <c r="D5" t="n">
-        <v>22.50361359553516</v>
+        <v>3.656837209274464</v>
       </c>
       <c r="E5" t="n">
-        <v>15.82582704376214</v>
+        <v>2.571696894611348</v>
       </c>
       <c r="F5" t="n">
-        <v>15.85860363360866</v>
+        <v>2.577023090461408</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.4906376674563</v>
+        <v>7.392228620961649</v>
       </c>
       <c r="D6" t="n">
-        <v>46.07572770453049</v>
+        <v>7.487305751986204</v>
       </c>
       <c r="E6" t="n">
-        <v>15.82582704376214</v>
+        <v>2.571696894611348</v>
       </c>
       <c r="F6" t="n">
-        <v>15.85860363360866</v>
+        <v>2.577023090461408</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.27734348435853</v>
+        <v>5.082568316208261</v>
       </c>
       <c r="D7" t="n">
-        <v>32.34069871310376</v>
+        <v>5.255363540879361</v>
       </c>
       <c r="E7" t="n">
-        <v>15.82582704376214</v>
+        <v>2.571696894611348</v>
       </c>
       <c r="F7" t="n">
-        <v>15.85860363360866</v>
+        <v>2.577023090461408</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>64.72756672473166</v>
+        <v>10.5182295927689</v>
       </c>
       <c r="D8" t="n">
-        <v>65.80736876196222</v>
+        <v>10.69369742381886</v>
       </c>
       <c r="E8" t="n">
-        <v>15.82582704376214</v>
+        <v>2.571696894611348</v>
       </c>
       <c r="F8" t="n">
-        <v>15.85860363360866</v>
+        <v>2.577023090461408</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.98779495756518</v>
+        <v>2.435516680604342</v>
       </c>
       <c r="D9" t="n">
-        <v>14.23174304181039</v>
+        <v>2.312658244294188</v>
       </c>
       <c r="E9" t="n">
-        <v>15.82582704376214</v>
+        <v>2.571696894611348</v>
       </c>
       <c r="F9" t="n">
-        <v>15.85860363360866</v>
+        <v>2.577023090461408</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
